--- a/Data_clean/MCAS/Estados_US/Edos_USA_2022/CONNECTICUT_2022.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2022/CONNECTICUT_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D484"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Jesús María</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -503,7 +528,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C10">
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Angel Albino Corzo</t>
@@ -527,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bejucal de Ocampo</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C12">
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -644,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>La Independencia</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -722,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C27">
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Pueblo Nuevo Solistahuacán</t>
@@ -787,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C32">
@@ -800,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Soyaló</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -839,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -865,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -891,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1010,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1023,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1038,7 +1243,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1067,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1093,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1215,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1228,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1241,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Poanas</t>
@@ -1254,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1269,7 +1549,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1285,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Almoloya de Alquisiras</t>
+          <t>Almoloya De Alquisiras</t>
         </is>
       </c>
       <c r="C68">
@@ -1298,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C69">
@@ -1311,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1324,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1337,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1350,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1363,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C74">
@@ -1376,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1389,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1402,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1415,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Jiquipilco</t>
@@ -1428,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1441,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1454,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C81">
@@ -1467,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1480,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Ocuilan</t>
@@ -1493,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C84">
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1545,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Tlalmanalco</t>
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1584,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Valle de Chalco Solidaridad</t>
+          <t>Valle De Chalco Solidaridad</t>
         </is>
       </c>
       <c r="C91">
@@ -1597,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -1610,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1623,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1643,7 +2058,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C95">
@@ -1654,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Atarjea</t>
@@ -1667,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1680,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1693,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>León</t>
@@ -1706,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1719,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -1732,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C102">
@@ -1745,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -1758,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -1771,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1784,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1804,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C107">
@@ -1815,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1828,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Alcozauca de Guerrero</t>
+          <t>Alcozauca De Guerrero</t>
         </is>
       </c>
       <c r="C109">
@@ -1841,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -1854,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Apaxtla</t>
@@ -1867,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -1880,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C113">
@@ -1893,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1906,9 +2411,14 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C115">
@@ -1919,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Cocula</t>
@@ -1932,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Copala</t>
@@ -1945,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1958,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Cuautepec</t>
@@ -1971,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Eduardo Neri</t>
@@ -1984,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -1997,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Huitzuco de los Figueroa</t>
+          <t>Huitzuco De Los Figueroa</t>
         </is>
       </c>
       <c r="C122">
@@ -2010,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -2023,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -2036,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -2049,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2062,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Petatlán</t>
@@ -2075,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -2088,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -2101,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -2114,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C131">
@@ -2127,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -2140,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C133">
@@ -2153,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tixtla de Guerrero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C134">
@@ -2166,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tlalixtaquilla de Maldonado</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C135">
@@ -2179,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C136">
@@ -2192,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -2205,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -2218,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -2231,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -2244,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2275,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -2288,9 +2933,14 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C144">
@@ -2301,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -2314,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -2327,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Nicolás Flores</t>
@@ -2340,9 +3005,14 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C148">
@@ -2353,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>San Salvador</t>
@@ -2366,9 +3041,14 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Santiago de Anaya</t>
+          <t>Santiago De Anaya</t>
         </is>
       </c>
       <c r="C150">
@@ -2379,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -2392,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Tlaxcoapan</t>
@@ -2405,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C153">
@@ -2418,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Xochicoatlán</t>
@@ -2431,9 +3131,14 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C155">
@@ -2444,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2475,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -2488,6 +3203,11 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2501,9 +3221,14 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C160">
@@ -2514,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -2527,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -2540,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>San Juanito de Escobedo</t>
+          <t>San Juanito De Escobedo</t>
         </is>
       </c>
       <c r="C163">
@@ -2553,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -2566,9 +3311,14 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C165">
@@ -2579,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Valle de Juárez</t>
+          <t>Valle De Juárez</t>
         </is>
       </c>
       <c r="C166">
@@ -2592,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C167">
@@ -2605,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2636,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -2649,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Cotija</t>
@@ -2662,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Huaniqueo</t>
@@ -2675,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Jiquilpan</t>
@@ -2684,10 +3469,15 @@
         <v>14</v>
       </c>
       <c r="D173">
-        <v>0.009790209790209791</v>
+        <v>0.009790209790209793</v>
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -2701,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -2714,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Los Reyes</t>
@@ -2727,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -2740,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Marcos Castellanos</t>
@@ -2753,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2766,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Peribán</t>
@@ -2779,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -2792,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Tangamandapio</t>
@@ -2805,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tiquicheo de Nicolás Romero</t>
+          <t>Tiquicheo De Nicolás Romero</t>
         </is>
       </c>
       <c r="C183">
@@ -2818,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -2831,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -2844,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -2857,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2870,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2883,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2896,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -2909,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2940,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Ayala</t>
@@ -2953,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2966,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -2979,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Jantetelco</t>
@@ -2992,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -3005,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Jonacatepec</t>
@@ -3018,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Miacatlán</t>
@@ -3031,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -3044,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -3057,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -3070,9 +3995,14 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Tetela del Volcán</t>
+          <t>Tetela Del Volcán</t>
         </is>
       </c>
       <c r="C203">
@@ -3083,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -3096,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3127,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3158,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -3171,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -3184,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3204,7 +4164,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C212">
@@ -3215,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Asunción Nochixtlán</t>
@@ -3228,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Calihualá</t>
@@ -3241,9 +4211,14 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Coicoyán de las Flores</t>
+          <t>Coicoyán De Las Flores</t>
         </is>
       </c>
       <c r="C215">
@@ -3254,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -3267,9 +4247,14 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C217">
@@ -3280,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C218">
@@ -3293,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -3306,9 +4301,14 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C220">
@@ -3319,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C221">
@@ -3332,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Monjas</t>
@@ -3345,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Nejapa de Madero</t>
+          <t>Nejapa De Madero</t>
         </is>
       </c>
       <c r="C223">
@@ -3358,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C224">
@@ -3371,9 +4391,14 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C225">
@@ -3384,9 +4409,14 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C226">
@@ -3397,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -3410,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>San Agustín Chayuco</t>
@@ -3423,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>San Agustín Loxicha</t>
@@ -3436,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -3449,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>San Antonino el Alto</t>
+          <t>San Antonino El Alto</t>
         </is>
       </c>
       <c r="C231">
@@ -3462,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>San Jacinto Tlacotepec</t>
@@ -3475,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>San José Ayuquila</t>
@@ -3488,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>San José Tenango</t>
@@ -3501,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3514,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>San Juan Colorado</t>
@@ -3527,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>San Juan Cotzocón</t>
@@ -3540,6 +4625,11 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>San Juan Juquila Vijanos</t>
@@ -3553,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>San Juan Teitipac</t>
@@ -3566,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>San Lorenzo Texmelúcan</t>
@@ -3579,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -3592,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>San Pedro Atoyac</t>
@@ -3605,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>San Pedro Mixtepec - Distr. 22 -</t>
@@ -3618,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>San Sebastián Tecomaxtlahuaca</t>
@@ -3631,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>San Sebastián Teitipac</t>
@@ -3644,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>San Vicente Lachixío</t>
@@ -3657,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Santa Catarina Loxicha</t>
@@ -3670,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Santa Cruz Xitla</t>
@@ -3683,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Santa Cruz Xoxocotlán</t>
@@ -3696,9 +4841,14 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Santa Inés del Monte</t>
+          <t>Santa Inés Del Monte</t>
         </is>
       </c>
       <c r="C250">
@@ -3709,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Santa Lucía Monteverde</t>
@@ -3722,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Santiago Chazumba</t>
@@ -3735,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -3748,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -3761,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Santiago Nacaltepec</t>
@@ -3774,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -3787,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Santiago Tetepec</t>
@@ -3800,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Santiago Yaitepec</t>
@@ -3813,9 +5003,14 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Tezoatlán de Segura y Luna</t>
+          <t>Tezoatlán De Segura Y Luna</t>
         </is>
       </c>
       <c r="C259">
@@ -3826,9 +5021,14 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C260">
@@ -3839,9 +5039,14 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Tlalixtac de Cabrera</t>
+          <t>Tlalixtac De Cabrera</t>
         </is>
       </c>
       <c r="C261">
@@ -3852,9 +5057,14 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Totontepec Villa de Morelos</t>
+          <t>Totontepec Villa De Morelos</t>
         </is>
       </c>
       <c r="C262">
@@ -3865,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Trinidad Zaachila</t>
@@ -3878,9 +5093,14 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Villa de Etla</t>
+          <t>Villa De Etla</t>
         </is>
       </c>
       <c r="C264">
@@ -3891,9 +5111,14 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Villa de Zaachila</t>
+          <t>Villa De Zaachila</t>
         </is>
       </c>
       <c r="C265">
@@ -3904,9 +5129,14 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Zapotitlán del Río</t>
+          <t>Zapotitlán Del Río</t>
         </is>
       </c>
       <c r="C266">
@@ -3917,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Zimatlán de Álvarez</t>
+          <t>Zimatlán De Álvarez</t>
         </is>
       </c>
       <c r="C267">
@@ -3930,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3961,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -3974,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Ahuehuetitla</t>
@@ -3987,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Albino Zertuche</t>
@@ -4000,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Aljojuca</t>
@@ -4013,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Amozoc</t>
@@ -4026,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -4039,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Atzitzihuacán</t>
@@ -4052,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Axutla</t>
@@ -4065,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Calpan</t>
@@ -4078,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -4091,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -4104,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -4117,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Chiconcuautla</t>
@@ -4130,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -4143,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -4156,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Chignautla</t>
@@ -4169,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -4182,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Coxcatlán</t>
@@ -4195,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Coyotepec</t>
@@ -4208,9 +5543,14 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cuapiaxtla de Madero</t>
+          <t>Cuapiaxtla De Madero</t>
         </is>
       </c>
       <c r="C289">
@@ -4221,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Cuautlancingo</t>
@@ -4234,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C291">
@@ -4247,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -4260,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -4273,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4286,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -4299,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -4312,9 +5687,14 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C297">
@@ -4325,9 +5705,14 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Huehuetlán el Grande</t>
+          <t>Huehuetlán El Grande</t>
         </is>
       </c>
       <c r="C298">
@@ -4338,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -4351,9 +5741,14 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Ixcamilpa de Guerrero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C300">
@@ -4364,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -4377,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C302">
@@ -4390,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Jalpan</t>
@@ -4403,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -4416,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Juan C. Bonilla</t>
@@ -4429,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Juan N. Méndez</t>
@@ -4442,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -4455,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -4468,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Ocoyucan</t>
@@ -4481,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Olintla</t>
@@ -4494,9 +5939,14 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Palmar de Bravo</t>
+          <t>Palmar De Bravo</t>
         </is>
       </c>
       <c r="C311">
@@ -4507,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>Pantepec</t>
@@ -4520,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>Petlalcingo</t>
@@ -4533,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -4546,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>Quecholac</t>
@@ -4559,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>Rafael Lara Grajales</t>
@@ -4572,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -4585,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>San Felipe Teotlalcingo</t>
@@ -4598,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>San Gabriel Chilac</t>
@@ -4611,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>San Gregorio Atzompa</t>
@@ -4624,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -4637,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>San Martín Totoltepec</t>
@@ -4650,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>San Matías Tlalancaleca</t>
@@ -4663,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>San Miguel Xoxtla</t>
@@ -4676,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -4689,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>San Pedro Yeloixtlahuaca</t>
@@ -4702,9 +6227,14 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>San Salvador el Seco</t>
+          <t>San Salvador El Seco</t>
         </is>
       </c>
       <c r="C327">
@@ -4715,9 +6245,14 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Salvador el Verde</t>
+          <t>San Salvador El Verde</t>
         </is>
       </c>
       <c r="C328">
@@ -4728,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -4741,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>Santo Tomás Hueyotlipan</t>
@@ -4754,9 +6299,14 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Tecali de Herrera</t>
+          <t>Tecali De Herrera</t>
         </is>
       </c>
       <c r="C331">
@@ -4767,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -4780,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Tecomatlán</t>
@@ -4793,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -4806,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -4815,10 +6385,15 @@
         <v>14</v>
       </c>
       <c r="D335">
-        <v>0.009790209790209791</v>
+        <v>0.009790209790209793</v>
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Teopantlán</t>
@@ -4832,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -4845,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Tepemaxalco</t>
@@ -4858,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Tepeojuma</t>
@@ -4871,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Tepetzintla</t>
@@ -4884,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Tepexco</t>
@@ -4897,9 +6497,14 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C342">
@@ -4910,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -4923,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -4936,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -4949,9 +6569,14 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C346">
@@ -4962,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -4975,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -4988,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Tlapanalá</t>
@@ -5001,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -5014,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -5027,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -5040,6 +6695,11 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -5053,6 +6713,11 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -5066,6 +6731,11 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
           <t>Tzicatlacoyan</t>
@@ -5079,6 +6749,11 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -5092,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Xicotepec</t>
@@ -5105,6 +6785,11 @@
       </c>
     </row>
     <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr">
         <is>
           <t>Xochiltepec</t>
@@ -5118,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Xochitlán Todos Santos</t>
@@ -5131,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -5144,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -5157,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -5170,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -5183,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -5196,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Zihuateutla</t>
@@ -5209,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5240,9 +6965,14 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C368">
@@ -5253,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -5266,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -5279,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5310,6 +7055,11 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5341,9 +7091,14 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Mexquitic de Carmona</t>
+          <t>Mexquitic De Carmona</t>
         </is>
       </c>
       <c r="C375">
@@ -5354,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -5367,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -5380,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -5393,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Tampamolón Corona</t>
@@ -5406,9 +7181,14 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tanquián de Escobedo</t>
+          <t>Tanquián De Escobedo</t>
         </is>
       </c>
       <c r="C380">
@@ -5419,9 +7199,14 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C381">
@@ -5432,6 +7217,11 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -5445,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5476,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -5489,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -5502,6 +7307,11 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
           <t>Mazatlán</t>
@@ -5515,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -5528,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5559,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -5572,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5603,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -5616,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -5629,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5660,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>San Fernando</t>
@@ -5673,9 +7523,14 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Soto la Marina</t>
+          <t>Soto La Marina</t>
         </is>
       </c>
       <c r="C399">
@@ -5686,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -5699,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Valle Hermoso</t>
@@ -5712,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -5725,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5756,6 +7631,11 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -5769,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -5782,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>El Carmen Tequexquitla</t>
@@ -5795,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -5808,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -5821,9 +7721,14 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C410">
@@ -5834,9 +7739,14 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Mazatecochco de José María Morelos</t>
+          <t>Mazatecochco De José María Morelos</t>
         </is>
       </c>
       <c r="C411">
@@ -5847,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Natívitas</t>
@@ -5860,9 +7775,14 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Papalotla de Xicohténcatl</t>
+          <t>Papalotla De Xicohténcatl</t>
         </is>
       </c>
       <c r="C413">
@@ -5873,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>San Francisco Tetlanohcan</t>
@@ -5886,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>San Jerónimo Zacualpan</t>
@@ -5899,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>San José Teacalco</t>
@@ -5912,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>San Juan Huactzinco</t>
@@ -5925,9 +7865,14 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>San Pablo del Monte</t>
+          <t>San Pablo Del Monte</t>
         </is>
       </c>
       <c r="C418">
@@ -5938,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Santa Apolonia Teacalco</t>
@@ -5951,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Santa Catarina Ayometla</t>
@@ -5964,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Santa Cruz Tlaxcala</t>
@@ -5977,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Santa Isabel Xiloxoxtla</t>
@@ -5990,6 +7955,11 @@
       </c>
     </row>
     <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B423" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -6003,6 +7973,11 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>Tepeyanco</t>
@@ -6016,6 +7991,11 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -6029,6 +8009,11 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
           <t>Tetlatlahuca</t>
@@ -6042,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -6055,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -6068,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Tocatlán</t>
@@ -6081,6 +8081,11 @@
       </c>
     </row>
     <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B430" t="inlineStr">
         <is>
           <t>Totolac</t>
@@ -6094,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>Xaloztoc</t>
@@ -6107,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -6120,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Xicohtzinco</t>
@@ -6133,6 +8153,11 @@
       </c>
     </row>
     <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B434" t="inlineStr">
         <is>
           <t>Yauhquemehcan</t>
@@ -6146,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -6159,6 +8189,11 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6190,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -6203,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Atlahuilco</t>
@@ -6216,9 +8261,14 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C440">
@@ -6229,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Carrillo Puerto</t>
@@ -6242,6 +8297,11 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
           <t>Catemaco</t>
@@ -6255,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>Cazones</t>
@@ -6268,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Coacoatzintla</t>
@@ -6281,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -6294,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -6307,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -6320,6 +8405,11 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
           <t>Coyutla</t>
@@ -6333,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -6346,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Fortín</t>
@@ -6359,6 +8459,11 @@
       </c>
     </row>
     <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B451" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -6372,9 +8477,14 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C452">
@@ -6385,9 +8495,14 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C453">
@@ -6398,9 +8513,14 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C454">
@@ -6411,6 +8531,11 @@
       </c>
     </row>
     <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -6424,9 +8549,14 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C456">
@@ -6437,6 +8567,11 @@
       </c>
     </row>
     <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B457" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -6450,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -6463,9 +8603,14 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C459">
@@ -6476,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -6489,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Nautla</t>
@@ -6502,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -6515,9 +8675,14 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Ozuluama de Mascareñas</t>
+          <t>Ozuluama De Mascareñas</t>
         </is>
       </c>
       <c r="C463">
@@ -6528,6 +8693,11 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -6541,9 +8711,14 @@
       </c>
     </row>
     <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Paso del Macho</t>
+          <t>Paso Del Macho</t>
         </is>
       </c>
       <c r="C465">
@@ -6554,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Perote</t>
@@ -6567,9 +8747,14 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C467">
@@ -6580,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -6593,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -6606,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Tatatila</t>
@@ -6619,6 +8819,11 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -6632,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -6645,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Tlaquilpa</t>
@@ -6658,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -6671,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Ursulo Galván</t>
@@ -6684,6 +8909,11 @@
       </c>
     </row>
     <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -6697,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -6710,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6741,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6772,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -6785,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6808,41 +9063,6 @@
       </c>
       <c r="D484">
         <v>1</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
